--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="D2">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="D3">
-        <v>173</v>
+        <v>306</v>
       </c>
       <c r="E3">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="G2">
         <v>5</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>117</v>
       </c>
       <c r="D3">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3">
         <v>426</v>
